--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_S_ADBZR_LTA-CSTD-0-06-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_S_ADBZR_LTA-CSTD-0-06-A-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.91.244.104\body-ph\DTPH資産(製品別)\グラフィック\業務管理\SINGLETASK_FY25\32_BEV_MCU_シス検ADAS向け_設計サポート\03_Output\07_Alertマクロ変更(ADBZR)\Dj\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\s10035azcfs0534.file.core.windows.net\metersoft\開発用\Toyota\BEV\設計成果物_MET\MCU-DT\02.Design\06.FF2\A1.要件\BEV3CDCMET-3653_S_ADBZR\01.パラメータ設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A5E255-E80A-4794-BF17-70AEBF160089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C3751F-B9D1-44A5-B4B0-60FA9227E09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-2250" windowWidth="29040" windowHeight="15720" tabRatio="774" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="774" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認）" sheetId="25" r:id="rId1"/>
@@ -5718,6 +5718,45 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5745,31 +5784,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5779,24 +5797,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5968,16 +5968,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>4483</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>164726</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>42582</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>72390</xdr:rowOff>
+      <xdr:rowOff>49978</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6007,8 +6007,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5067300" y="7772400"/>
-          <a:ext cx="495300" cy="567690"/>
+          <a:off x="5719483" y="7605432"/>
+          <a:ext cx="542364" cy="557605"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6031,16 +6031,16 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
-          <xdr:col>35</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
+          <xdr:col>36</xdr:col>
+          <xdr:colOff>2242</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>34290</xdr:rowOff>
+          <xdr:rowOff>26894</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>39</xdr:col>
-          <xdr:colOff>1085</xdr:colOff>
+          <xdr:colOff>56030</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>11430</xdr:rowOff>
+          <xdr:rowOff>7844</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6050,7 +6050,7 @@
                   <a14:compatExt spid="_x0000_s33795"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E78222C0-6560-7EA7-C1B6-E5022F385109}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003840000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6068,7 +6068,6 @@
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
             <a:extLst>
               <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
                 <a14:hiddenFill>
@@ -6082,20 +6081,10 @@
                   <a:solidFill>
                     <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
                   </a:solidFill>
-                  <a:prstDash val="solid"/>
                   <a:miter lim="800000"/>
                   <a:headEnd/>
-                  <a:tailEnd type="none" w="med" len="med"/>
+                  <a:tailEnd/>
                 </a14:hiddenLine>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="808080"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
               </a:ext>
             </a:extLst>
           </xdr:spPr>
@@ -7718,7 +7707,7 @@
         <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{829489CA-448F-2654-0D5A-BB1491939382}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7772,7 +7761,7 @@
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FC16F6D-E04F-3B95-301B-B1945EF9AF59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7826,7 +7815,7 @@
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8712B10-4B28-8B5A-E7EA-0316B312AB80}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8600,58 +8589,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>500063</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>164102</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>75</xdr:col>
-      <xdr:colOff>249993</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>86552</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="図 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-00000F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="36980813" y="4664665"/>
-          <a:ext cx="15847180" cy="5351700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>594103</xdr:colOff>
+      <xdr:colOff>661146</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>73045</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
-      <xdr:colOff>477355</xdr:colOff>
+      <xdr:colOff>369794</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>20250</xdr:rowOff>
     </xdr:to>
@@ -8668,8 +8613,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20835737" y="4779516"/>
-          <a:ext cx="10767749" cy="273856"/>
+          <a:off x="23229793" y="4779516"/>
+          <a:ext cx="11811001" cy="283381"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8855,13 +8800,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>35</xdr:col>
-      <xdr:colOff>177964</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>58559</xdr:rowOff>
+      <xdr:colOff>212912</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>36</xdr:col>
-      <xdr:colOff>84346</xdr:colOff>
+      <xdr:colOff>33618</xdr:colOff>
       <xdr:row>78</xdr:row>
       <xdr:rowOff>122464</xdr:rowOff>
     </xdr:to>
@@ -8878,8 +8823,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27909321" y="10780988"/>
-          <a:ext cx="518704" cy="7411762"/>
+          <a:off x="30849794" y="10421471"/>
+          <a:ext cx="493059" cy="7148552"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8921,15 +8866,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>256360</xdr:colOff>
+      <xdr:colOff>177919</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>82555</xdr:rowOff>
+      <xdr:rowOff>71349</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
-      <xdr:colOff>181314</xdr:colOff>
+      <xdr:colOff>102873</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>136145</xdr:rowOff>
+      <xdr:rowOff>124939</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8944,8 +8889,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26763074" y="11335662"/>
-          <a:ext cx="1149597" cy="407376"/>
+          <a:off x="29470095" y="10806584"/>
+          <a:ext cx="1269660" cy="389767"/>
         </a:xfrm>
         <a:prstGeom prst="borderCallout1">
           <a:avLst>
@@ -9013,13 +8958,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>43</xdr:col>
-      <xdr:colOff>203466</xdr:colOff>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>86</xdr:row>
-      <xdr:rowOff>68224</xdr:rowOff>
+      <xdr:rowOff>67234</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>48</xdr:col>
-      <xdr:colOff>129174</xdr:colOff>
+      <xdr:colOff>201705</xdr:colOff>
       <xdr:row>87</xdr:row>
       <xdr:rowOff>139975</xdr:rowOff>
     </xdr:to>
@@ -9036,8 +8981,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="32820379" y="19300441"/>
-          <a:ext cx="2990273" cy="245686"/>
+          <a:off x="36206206" y="18859499"/>
+          <a:ext cx="3372970" cy="240829"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9079,15 +9024,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>43</xdr:col>
-      <xdr:colOff>221120</xdr:colOff>
+      <xdr:colOff>168088</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>145762</xdr:rowOff>
+      <xdr:rowOff>123265</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>48</xdr:col>
-      <xdr:colOff>177308</xdr:colOff>
+      <xdr:colOff>212911</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>5846</xdr:rowOff>
+      <xdr:rowOff>11206</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9102,8 +9047,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="32838033" y="19551914"/>
-          <a:ext cx="3020753" cy="207954"/>
+          <a:off x="36183794" y="19083618"/>
+          <a:ext cx="3406588" cy="224117"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9168,15 +9113,15 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="37151049" y="18480439"/>
-          <a:ext cx="1686479" cy="780429"/>
+          <a:off x="40965921" y="18069720"/>
+          <a:ext cx="1864799" cy="751196"/>
         </a:xfrm>
         <a:prstGeom prst="borderCallout1">
           <a:avLst>
             <a:gd name="adj1" fmla="val 59203"/>
             <a:gd name="adj2" fmla="val -288"/>
-            <a:gd name="adj3" fmla="val 107365"/>
-            <a:gd name="adj4" fmla="val -119552"/>
+            <a:gd name="adj3" fmla="val 99906"/>
+            <a:gd name="adj4" fmla="val -117148"/>
           </a:avLst>
         </a:prstGeom>
         <a:solidFill>
@@ -9279,15 +9224,15 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="37128970" y="19996429"/>
-          <a:ext cx="1609668" cy="850074"/>
+          <a:off x="40943842" y="19533090"/>
+          <a:ext cx="1728548" cy="820842"/>
         </a:xfrm>
         <a:prstGeom prst="borderCallout1">
           <a:avLst>
             <a:gd name="adj1" fmla="val 59203"/>
             <a:gd name="adj2" fmla="val -288"/>
-            <a:gd name="adj3" fmla="val -31053"/>
-            <a:gd name="adj4" fmla="val -125670"/>
+            <a:gd name="adj3" fmla="val -26957"/>
+            <a:gd name="adj4" fmla="val -126967"/>
           </a:avLst>
         </a:prstGeom>
         <a:solidFill>
@@ -12439,9 +12384,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EB9570-3F95-4189-84D4-A6E0EACD4E4D}">
   <dimension ref="A1:AN49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="40" width="2.21875" style="229" customWidth="1"/>
+    <col min="1" max="40" width="2.25" style="229" customWidth="1"/>
     <col min="41" max="16384" width="9" style="229"/>
   </cols>
   <sheetData>
@@ -14569,16 +14514,16 @@
           <objectPr defaultSize="0" autoPict="0" r:id="rId5">
             <anchor>
               <from>
-                <xdr:col>35</xdr:col>
-                <xdr:colOff>114300</xdr:colOff>
+                <xdr:col>36</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>45</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
+                <xdr:rowOff>28575</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>39</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
+                <xdr:colOff>57150</xdr:colOff>
                 <xdr:row>48</xdr:row>
-                <xdr:rowOff>15240</xdr:rowOff>
+                <xdr:rowOff>9525</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -14596,14 +14541,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.8" thickBot="1">
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
       <c r="B2" s="56" t="s">
         <v>86</v>
       </c>
@@ -14613,7 +14558,7 @@
       </c>
       <c r="D2" s="57"/>
     </row>
-    <row r="3" spans="2:4" ht="13.8" thickBot="1">
+    <row r="3" spans="2:4" ht="14.25" thickBot="1">
       <c r="B3" s="50" t="s">
         <v>84</v>
       </c>
@@ -14624,7 +14569,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.8" thickTop="1">
+    <row r="4" spans="2:4" ht="14.25" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -14635,7 +14580,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39.6">
+    <row r="5" spans="2:4" ht="40.5">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -14646,7 +14591,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26.4">
+    <row r="6" spans="2:4" ht="27">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -14657,7 +14602,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52.8">
+    <row r="7" spans="2:4" ht="54">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -14668,7 +14613,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="79.2">
+    <row r="8" spans="2:4" ht="81">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -14690,7 +14635,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26.4">
+    <row r="10" spans="2:4" ht="27">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -14701,7 +14646,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26.4">
+    <row r="11" spans="2:4" ht="27">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -14712,7 +14657,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26.4">
+    <row r="12" spans="2:4" ht="27">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -14723,7 +14668,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26.4">
+    <row r="13" spans="2:4" ht="27">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -14734,7 +14679,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26.4">
+    <row r="14" spans="2:4" ht="27">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -14745,7 +14690,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="132">
+    <row r="15" spans="2:4" ht="135">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -14767,7 +14712,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26.4">
+    <row r="17" spans="2:4" ht="27">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -14778,7 +14723,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="92.4">
+    <row r="18" spans="2:4" ht="67.5">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -14789,7 +14734,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39.6">
+    <row r="19" spans="2:4" ht="40.5">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -14822,7 +14767,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26.4">
+    <row r="22" spans="2:4" ht="27">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -14833,7 +14778,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="26.4">
+    <row r="23" spans="2:4" ht="27">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -14844,7 +14789,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="92.4">
+    <row r="24" spans="2:4" ht="94.5">
       <c r="B24" s="2">
         <v>20</v>
       </c>
@@ -14865,7 +14810,7 @@
       <c r="C26" s="60"/>
       <c r="D26" s="49"/>
     </row>
-    <row r="27" spans="2:4" ht="13.8" thickBot="1">
+    <row r="27" spans="2:4" ht="14.25" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="61"/>
       <c r="D27" s="5"/>
@@ -14883,9 +14828,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387E0655-10E6-4ACC-B8DD-03565E855A85}">
   <dimension ref="B2:C56"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -15069,15 +15014,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X14"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.44140625" customWidth="1"/>
-    <col min="5" max="6" width="12.77734375" customWidth="1"/>
-    <col min="7" max="18" width="13.109375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="18" width="13.125" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -15147,7 +15092,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="13.8" thickBot="1"/>
+    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
       <c r="C7" s="273" t="s">
         <v>0</v>
@@ -15182,7 +15127,7 @@
       <c r="W7" s="271"/>
       <c r="X7" s="272"/>
     </row>
-    <row r="8" spans="2:24" ht="27" thickBot="1">
+    <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>92</v>
       </c>
@@ -15253,7 +15198,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="299.39999999999998" customHeight="1" thickTop="1">
+    <row r="9" spans="2:24" ht="299.45" customHeight="1" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -15325,7 +15270,7 @@
         <v>45236</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="211.2">
+    <row r="10" spans="2:24" ht="216">
       <c r="B10" s="9">
         <f t="shared" ref="B10" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
@@ -15389,7 +15334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="118.8">
+    <row r="11" spans="2:24" ht="121.5">
       <c r="B11" s="9">
         <f t="shared" ref="B11:B14" si="1">IF(C11=0,0,ROW()-ROW($B$8))</f>
         <v>3</v>
@@ -15493,7 +15438,7 @@
       <c r="W13" s="1"/>
       <c r="X13" s="214"/>
     </row>
-    <row r="14" spans="2:24" ht="13.8" thickBot="1">
+    <row r="14" spans="2:24" ht="14.25" thickBot="1">
       <c r="B14" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -15544,11 +15489,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.6640625" customWidth="1"/>
-    <col min="3" max="3" width="3.44140625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15562,13 +15507,13 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.8" thickBot="1">
+    <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="118" t="s">
         <v>135</v>
       </c>
       <c r="C6" s="118"/>
     </row>
-    <row r="7" spans="2:5" ht="13.8" thickBot="1">
+    <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="50" t="s">
         <v>137</v>
       </c>
@@ -15593,7 +15538,7 @@
       <c r="D9" s="130"/>
       <c r="E9" s="129"/>
     </row>
-    <row r="10" spans="2:5" ht="13.8" thickBot="1">
+    <row r="10" spans="2:5" ht="14.25" thickBot="1">
       <c r="C10" s="126"/>
       <c r="D10" s="217"/>
       <c r="E10" s="5"/>
@@ -15601,14 +15546,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="124"/>
     </row>
-    <row r="12" spans="2:5" ht="13.8" thickBot="1">
+    <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="119" t="s">
         <v>136</v>
       </c>
       <c r="C12" s="57"/>
       <c r="D12" s="57"/>
     </row>
-    <row r="13" spans="2:5" ht="13.8" thickBot="1">
+    <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="120"/>
       <c r="C13" s="125" t="s">
         <v>137</v>
@@ -15620,7 +15565,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.8" thickTop="1">
+    <row r="14" spans="2:5" ht="14.25" thickTop="1">
       <c r="C14" s="122">
         <v>0</v>
       </c>
@@ -15697,17 +15642,17 @@
         <v>176</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.8" thickBot="1">
+    <row r="21" spans="2:5" ht="14.25" thickBot="1">
       <c r="C21" s="126"/>
       <c r="D21" s="61"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="13.8" thickBot="1">
+    <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="118" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.8" thickBot="1">
+    <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="125" t="s">
         <v>137</v>
       </c>
@@ -15794,12 +15739,12 @@
       <c r="D33" s="60"/>
       <c r="E33" s="49"/>
     </row>
-    <row r="34" spans="2:5" ht="13.8" thickBot="1">
+    <row r="34" spans="2:5" ht="14.25" thickBot="1">
       <c r="C34" s="126"/>
       <c r="D34" s="61"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="13.8" thickBot="1">
+    <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="118" t="s">
         <v>172</v>
       </c>
@@ -15811,7 +15756,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.8" thickBot="1">
+    <row r="39" spans="2:5" ht="14.25" thickBot="1">
       <c r="C39" s="280"/>
       <c r="D39" s="281"/>
       <c r="E39" s="5" t="s">
@@ -15841,131 +15786,131 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N35"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.77734375" customWidth="1"/>
-    <col min="9" max="9" width="20.88671875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.8" thickBot="1"/>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="294" t="s">
+      <c r="B2" s="304" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="295"/>
-      <c r="D2" s="282" t="s">
+      <c r="C2" s="305"/>
+      <c r="D2" s="295" t="s">
         <v>285</v>
       </c>
-      <c r="E2" s="283"/>
-      <c r="F2" s="283"/>
-      <c r="G2" s="283"/>
-      <c r="H2" s="284"/>
+      <c r="E2" s="296"/>
+      <c r="F2" s="296"/>
+      <c r="G2" s="296"/>
+      <c r="H2" s="297"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="296" t="s">
+      <c r="B3" s="282" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="297"/>
-      <c r="D3" s="300" t="s">
+      <c r="C3" s="283"/>
+      <c r="D3" s="306" t="s">
         <v>286</v>
       </c>
-      <c r="E3" s="301"/>
-      <c r="F3" s="301"/>
-      <c r="G3" s="301"/>
-      <c r="H3" s="302"/>
+      <c r="E3" s="307"/>
+      <c r="F3" s="307"/>
+      <c r="G3" s="307"/>
+      <c r="H3" s="308"/>
     </row>
-    <row r="4" spans="2:14" ht="13.8" thickBot="1">
-      <c r="B4" s="298" t="s">
+    <row r="4" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B4" s="293" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="299"/>
-      <c r="D4" s="285" t="str">
+      <c r="C4" s="294"/>
+      <c r="D4" s="298" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_S_ADBZR_LTA-CSTD-0-06-A-C0.c</v>
       </c>
-      <c r="E4" s="286"/>
-      <c r="F4" s="286"/>
-      <c r="G4" s="286"/>
-      <c r="H4" s="287"/>
+      <c r="E4" s="299"/>
+      <c r="F4" s="299"/>
+      <c r="G4" s="299"/>
+      <c r="H4" s="300"/>
     </row>
-    <row r="5" spans="2:14" ht="13.8" thickBot="1">
+    <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="294" t="s">
+      <c r="B6" s="304" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="295"/>
-      <c r="D6" s="288" t="str">
+      <c r="C6" s="305"/>
+      <c r="D6" s="301" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>S_ADBZR_LTA</v>
       </c>
-      <c r="E6" s="289"/>
-      <c r="F6" s="289"/>
-      <c r="G6" s="289"/>
-      <c r="H6" s="290"/>
+      <c r="E6" s="302"/>
+      <c r="F6" s="302"/>
+      <c r="G6" s="302"/>
+      <c r="H6" s="303"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="296" t="s">
+      <c r="B7" s="282" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="297"/>
-      <c r="D7" s="291">
+      <c r="C7" s="283"/>
+      <c r="D7" s="284">
         <f>COUNTA($D$13:$D$35)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="292"/>
-      <c r="F7" s="292"/>
-      <c r="G7" s="292"/>
-      <c r="H7" s="293"/>
+      <c r="E7" s="285"/>
+      <c r="F7" s="285"/>
+      <c r="G7" s="285"/>
+      <c r="H7" s="286"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="296" t="s">
+      <c r="B8" s="282" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="297"/>
-      <c r="D8" s="291" t="str">
+      <c r="C8" s="283"/>
+      <c r="D8" s="284" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_S_ADBZR_LTA_MTRX</v>
       </c>
-      <c r="E8" s="292"/>
-      <c r="F8" s="292"/>
-      <c r="G8" s="292"/>
-      <c r="H8" s="293"/>
+      <c r="E8" s="285"/>
+      <c r="F8" s="285"/>
+      <c r="G8" s="285"/>
+      <c r="H8" s="286"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="296" t="s">
+      <c r="B9" s="282" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="297"/>
-      <c r="D9" s="303" t="s">
+      <c r="C9" s="283"/>
+      <c r="D9" s="287" t="s">
         <v>210</v>
       </c>
-      <c r="E9" s="304"/>
-      <c r="F9" s="304"/>
-      <c r="G9" s="304"/>
-      <c r="H9" s="305"/>
+      <c r="E9" s="288"/>
+      <c r="F9" s="288"/>
+      <c r="G9" s="288"/>
+      <c r="H9" s="289"/>
     </row>
-    <row r="10" spans="2:14" ht="13.8" thickBot="1">
-      <c r="B10" s="298" t="s">
+    <row r="10" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B10" s="293" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="299"/>
-      <c r="D10" s="306"/>
-      <c r="E10" s="307"/>
-      <c r="F10" s="307"/>
-      <c r="G10" s="307"/>
-      <c r="H10" s="308"/>
+      <c r="C10" s="294"/>
+      <c r="D10" s="290"/>
+      <c r="E10" s="291"/>
+      <c r="F10" s="291"/>
+      <c r="G10" s="291"/>
+      <c r="H10" s="292"/>
     </row>
-    <row r="11" spans="2:14" ht="13.8" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.8" thickBot="1">
+    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1">
       <c r="B12" s="109" t="s">
         <v>34</v>
       </c>
@@ -16000,7 +15945,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.8" thickTop="1">
+    <row r="13" spans="2:14" ht="14.25" thickTop="1">
       <c r="B13" s="78">
         <v>1</v>
       </c>
@@ -16789,7 +16734,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="2:14" ht="13.8" thickBot="1">
+    <row r="35" spans="2:14" ht="14.25" thickBot="1">
       <c r="B35" s="69">
         <v>23</v>
       </c>
@@ -16832,12 +16777,6 @@
     <protectedRange sqref="C13:E16" name="編集許可_2"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="D6:H6"/>
@@ -16848,6 +16787,12 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C35">
@@ -16893,21 +16838,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.44140625" customWidth="1"/>
-    <col min="6" max="6" width="52.77734375" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.88671875" customWidth="1"/>
-    <col min="16" max="16" width="9.88671875" customWidth="1"/>
-    <col min="17" max="17" width="44.6640625" customWidth="1"/>
-    <col min="18" max="18" width="73.6640625" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.8" thickBot="1">
+    <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
         <v>199</v>
       </c>
@@ -16915,7 +16860,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.8" thickBot="1">
+    <row r="3" spans="2:18" ht="14.25" thickBot="1">
       <c r="B3" s="109" t="s">
         <v>34</v>
       </c>
@@ -16953,7 +16898,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.8" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B4" s="131">
         <v>0</v>
       </c>
@@ -16981,7 +16926,7 @@
       </c>
       <c r="R4" s="108"/>
     </row>
-    <row r="5" spans="2:18" ht="13.8" thickTop="1">
+    <row r="5" spans="2:18" ht="14.25" thickTop="1">
       <c r="B5" s="134">
         <v>1</v>
       </c>
@@ -17509,7 +17454,7 @@
       <c r="Q28" s="113"/>
       <c r="R28" s="87"/>
     </row>
-    <row r="29" spans="2:18" ht="13.8" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="135">
         <v>25</v>
       </c>
@@ -17531,7 +17476,7 @@
       <c r="Q29" s="111"/>
       <c r="R29" s="89"/>
     </row>
-    <row r="32" spans="2:18" ht="13.8" thickBot="1">
+    <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
         <v>200</v>
       </c>
@@ -17539,7 +17484,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.8" thickBot="1">
+    <row r="33" spans="2:18" ht="14.25" thickBot="1">
       <c r="B33" s="109" t="s">
         <v>34</v>
       </c>
@@ -17571,7 +17516,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.8" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B34" s="131">
         <v>0</v>
       </c>
@@ -17597,7 +17542,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.8" thickTop="1">
+    <row r="35" spans="2:18" ht="14.25" thickTop="1">
       <c r="B35" s="134">
         <v>1</v>
       </c>
@@ -18125,7 +18070,7 @@
       <c r="Q58" s="113"/>
       <c r="R58" s="136"/>
     </row>
-    <row r="59" spans="2:18" ht="13.8" thickBot="1">
+    <row r="59" spans="2:18" ht="14.25" thickBot="1">
       <c r="B59" s="135">
         <v>25</v>
       </c>
@@ -18176,29 +18121,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U89"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="29.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="29.125" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" customWidth="1"/>
-    <col min="10" max="10" width="41.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="16.109375" customWidth="1"/>
-    <col min="14" max="14" width="43.77734375" customWidth="1"/>
-    <col min="15" max="15" width="57.109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="41.625" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="43.75" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.8" thickBot="1">
+    <row r="1" spans="2:21" ht="14.25" thickBot="1">
       <c r="C1" s="63" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.8" thickBot="1">
+    <row r="2" spans="2:21" ht="14.25" thickBot="1">
       <c r="B2" s="70" t="s">
         <v>58</v>
       </c>
@@ -18242,7 +18187,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14.4" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="23"/>
       <c r="C3" s="30" t="s">
         <v>109</v>
@@ -18263,7 +18208,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.8" thickTop="1">
+    <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="80" t="s">
         <v>296</v>
       </c>
@@ -18597,7 +18542,7 @@
       </c>
       <c r="U12" s="24"/>
     </row>
-    <row r="13" spans="2:21" ht="13.8" thickBot="1">
+    <row r="13" spans="2:21" ht="14.25" thickBot="1">
       <c r="B13" s="80"/>
       <c r="C13" s="79"/>
       <c r="D13" s="91"/>
@@ -20498,7 +20443,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="89" spans="2:15" ht="13.8" thickBot="1">
+    <row r="89" spans="2:15" ht="14.25" thickBot="1">
       <c r="B89" s="32"/>
       <c r="C89" s="33"/>
       <c r="D89" s="88"/>
@@ -20571,18 +20516,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.109375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6640625" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.109375" customWidth="1"/>
-    <col min="48" max="48" width="23.6640625" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20808,7 +20753,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.8" thickBot="1">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
       <c r="A4" s="313" t="s">
         <v>63</v>
       </c>
@@ -20856,7 +20801,7 @@
       <c r="AV4" s="53"/>
       <c r="AW4" s="54"/>
     </row>
-    <row r="5" spans="1:49" ht="13.8" thickBot="1">
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
       <c r="A5" s="315"/>
       <c r="B5" s="316"/>
       <c r="C5" s="152"/>
@@ -22359,7 +22304,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.8" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="105"/>
       <c r="C17" s="26">
         <f t="shared" si="2"/>
@@ -28729,7 +28674,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.8" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="35" t="s">
         <v>64</v>
       </c>
@@ -49357,18 +49302,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.109375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6640625" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.109375" customWidth="1"/>
-    <col min="48" max="48" width="23.6640625" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -49590,7 +49535,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.8" thickBot="1">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
       <c r="A4" s="313" t="s">
         <v>63</v>
       </c>
@@ -49638,7 +49583,7 @@
       <c r="AV4" s="53"/>
       <c r="AW4" s="54"/>
     </row>
-    <row r="5" spans="1:49" ht="13.8" thickBot="1">
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
       <c r="A5" s="315"/>
       <c r="B5" s="316"/>
       <c r="C5" s="157"/>
@@ -51155,7 +51100,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.8" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="105"/>
       <c r="C17" s="26">
         <f t="shared" si="2"/>
@@ -57535,7 +57480,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.8" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="35" t="s">
         <v>64</v>
       </c>
@@ -78153,23 +78098,23 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CBE6902-79C4-4E3B-BE36-D46BF98B5E94}">
   <dimension ref="B37:BH132"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="159"/>
-    <col min="2" max="2" width="68.21875" style="159" customWidth="1"/>
-    <col min="3" max="3" width="5.21875" style="159" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.33203125" style="159" customWidth="1"/>
-    <col min="5" max="10" width="3.44140625" style="159" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.21875" style="159" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="40.88671875" style="159" customWidth="1"/>
-    <col min="13" max="13" width="27.6640625" style="159" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.109375" style="159" customWidth="1"/>
-    <col min="15" max="15" width="16.33203125" style="159" customWidth="1"/>
-    <col min="16" max="16" width="7.21875" style="159" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.88671875" style="159" customWidth="1"/>
-    <col min="18" max="80" width="8.88671875" style="159"/>
-    <col min="81" max="89" width="8.88671875" style="159" customWidth="1"/>
-    <col min="90" max="16384" width="8.88671875" style="159"/>
+    <col min="1" max="1" width="8.875" style="159"/>
+    <col min="2" max="2" width="68.25" style="159" customWidth="1"/>
+    <col min="3" max="3" width="5.25" style="159" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.375" style="159" customWidth="1"/>
+    <col min="5" max="10" width="3.5" style="159" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.25" style="159" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40.875" style="159" customWidth="1"/>
+    <col min="13" max="13" width="27.625" style="159" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.125" style="159" customWidth="1"/>
+    <col min="15" max="15" width="16.375" style="159" customWidth="1"/>
+    <col min="16" max="16" width="7.25" style="159" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.875" style="159" customWidth="1"/>
+    <col min="18" max="80" width="8.875" style="159"/>
+    <col min="81" max="89" width="8.875" style="159" customWidth="1"/>
+    <col min="90" max="16384" width="8.875" style="159"/>
   </cols>
   <sheetData>
     <row r="37" spans="2:17" ht="15" thickBot="1">
@@ -78297,7 +78242,7 @@
       <c r="P41" s="173"/>
       <c r="Q41" s="174"/>
     </row>
-    <row r="42" spans="2:17" ht="26.4">
+    <row r="42" spans="2:17" ht="27">
       <c r="B42" s="175" t="s">
         <v>28</v>
       </c>
@@ -78323,7 +78268,7 @@
       <c r="P42" s="173"/>
       <c r="Q42" s="142"/>
     </row>
-    <row r="43" spans="2:17" ht="133.19999999999999">
+    <row r="43" spans="2:17" ht="136.5">
       <c r="B43" s="167" t="s">
         <v>29</v>
       </c>
@@ -78365,7 +78310,7 @@
       <c r="P43" s="173"/>
       <c r="Q43" s="174"/>
     </row>
-    <row r="44" spans="2:17" ht="40.200000000000003" thickBot="1">
+    <row r="44" spans="2:17" ht="27.75" thickBot="1">
       <c r="B44" s="180" t="s">
         <v>30</v>
       </c>
@@ -78409,7 +78354,7 @@
       </c>
       <c r="Q44" s="186"/>
     </row>
-    <row r="45" spans="2:17" ht="13.8" thickTop="1">
+    <row r="45" spans="2:17" ht="14.25" thickTop="1">
       <c r="B45" s="187" t="s">
         <v>231</v>
       </c>
@@ -78541,7 +78486,7 @@
       </c>
       <c r="Q47" s="200"/>
     </row>
-    <row r="48" spans="2:17" ht="13.8" thickBot="1">
+    <row r="48" spans="2:17" ht="14.25" thickBot="1">
       <c r="B48" s="203" t="s">
         <v>206</v>
       </c>
@@ -78710,7 +78655,7 @@
       <c r="P62" s="173"/>
       <c r="Q62" s="174"/>
     </row>
-    <row r="63" spans="2:17" ht="26.4">
+    <row r="63" spans="2:17" ht="27">
       <c r="B63" s="175" t="s">
         <v>28</v>
       </c>
@@ -78736,7 +78681,7 @@
       <c r="P63" s="173"/>
       <c r="Q63" s="142"/>
     </row>
-    <row r="64" spans="2:17" ht="133.19999999999999">
+    <row r="64" spans="2:17" ht="136.5">
       <c r="B64" s="167" t="s">
         <v>29</v>
       </c>
@@ -78778,7 +78723,7 @@
       <c r="P64" s="173"/>
       <c r="Q64" s="174"/>
     </row>
-    <row r="65" spans="2:17" ht="53.4" thickBot="1">
+    <row r="65" spans="2:17" ht="54.75" thickBot="1">
       <c r="B65" s="180" t="s">
         <v>30</v>
       </c>
@@ -78822,7 +78767,7 @@
       </c>
       <c r="Q65" s="186"/>
     </row>
-    <row r="66" spans="2:17" ht="13.8" thickTop="1">
+    <row r="66" spans="2:17" ht="14.25" thickTop="1">
       <c r="B66" s="187" t="s">
         <v>231</v>
       </c>
@@ -79130,7 +79075,7 @@
       </c>
       <c r="Q72" s="202"/>
     </row>
-    <row r="73" spans="2:17" ht="13.8" thickBot="1">
+    <row r="73" spans="2:17" ht="14.25" thickBot="1">
       <c r="B73" s="203" t="s">
         <v>206</v>
       </c>
